--- a/artfynd/A 38597-2022 artfynd.xlsx
+++ b/artfynd/A 38597-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38597-2022 artfynd.xlsx
+++ b/artfynd/A 38597-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14619844</v>
+        <v>15196324</v>
       </c>
       <c r="B8" t="n">
-        <v>42704</v>
+        <v>42705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>695692.8128370701</v>
+        <v>695694.0791200444</v>
       </c>
       <c r="R8" t="n">
-        <v>6657930.441980593</v>
+        <v>6657925.499482274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-08-26</t>
+          <t>2011-08-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-09-03</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1600,14 +1600,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elisabeth Hedin, Jan-Olov Björklund</t>
+          <t>Elisabeth Hedin, Nina Söderström, Jan-Olov Björklund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15196324</v>
+        <v>55768481</v>
       </c>
       <c r="B9" t="n">
         <v>42705</v>
@@ -1640,9 +1640,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1650,24 +1651,19 @@
           <t>larv/nymf</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Ununge och Edebo församlingar, Upl</t>
+          <t>Gillberga, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>695694.0791200444</v>
+        <v>695351.9560400967</v>
       </c>
       <c r="R9" t="n">
-        <v>6657925.499482274</v>
+        <v>6658150.300673919</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1691,7 +1687,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-08-16</t>
+          <t>2015-08-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1701,7 +1697,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2015-08-27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1709,41 +1705,31 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Inventeringen utfördes för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Stockholms län.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Hyggen med uppväxande ask och olvon</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elisabeth Hedin</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elisabeth Hedin, Nina Söderström, Jan-Olov Björklund</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55768481</v>
+        <v>89116280</v>
       </c>
       <c r="B10" t="n">
         <v>42705</v>
@@ -1776,7 +1762,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>kolonier</t>
@@ -1789,17 +1779,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gillberga, Upl</t>
+          <t>Gillberga och hygge Ö Karlaplan, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>695351.9560400967</v>
+        <v>695429.9189554056</v>
       </c>
       <c r="R10" t="n">
-        <v>6658150.300673919</v>
+        <v>6658127.887351463</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1823,7 +1813,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-08-27</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1833,7 +1823,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-08-27</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1842,33 +1832,52 @@
         </is>
       </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Mattias Lif, Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89116280</v>
+        <v>111675779</v>
       </c>
       <c r="B11" t="n">
-        <v>42705</v>
+        <v>42708</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1900,7 +1909,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1913,19 +1922,29 @@
           <t>larv/nymf</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gillberga och hygge Ö Karlaplan, Upl</t>
+          <t>Norrtälje kommun, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>695429.9189554056</v>
+        <v>695427</v>
       </c>
       <c r="R11" t="n">
-        <v>6658127.887351463</v>
+        <v>6658127</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1949,22 +1968,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nedblåst ask som skjuter skott.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1975,31 +1989,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Julia Stigenberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Lif, Jan-Olov Björklund</t>
+          <t>Julia Stigenberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2010,10 +2009,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96850439</v>
+        <v>116227965</v>
       </c>
       <c r="B12" t="n">
-        <v>42705</v>
+        <v>83113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2022,25 +2021,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100943</v>
+        <v>1444</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2050,27 +2049,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gillberga och hygge Ö Karlaplan, Upl</t>
+          <t>Skälbykärret (Fäbro V-ut), Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>695429.3920629226</v>
+        <v>695825</v>
       </c>
       <c r="R12" t="n">
-        <v>6658128.360336048</v>
+        <v>6657810</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2094,22 +2090,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2118,309 +2114,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gallrad, dikad sumpskog med enstaka Picea abies och Betula pubescens.</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>111675779</v>
-      </c>
-      <c r="B13" t="n">
-        <v>42708</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100943</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Asknätfjäril</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Euphydryas maturna</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Norrtälje kommun, Upl</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>695427</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6658127</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Edebo</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-08-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Nedblåst ask som skjuter skott.</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Julia Stigenberg</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Julia Stigenberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>116227965</v>
-      </c>
-      <c r="B14" t="n">
-        <v>83113</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1444</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Scharlakansvårskål agg.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Skälbykärret (Fäbro V-ut), Upl</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>695825</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6657810</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Edebo</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:24</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-04-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Gallrad, dikad sumpskog med enstaka Picea abies och Betula pubescens.</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
         </is>
